--- a/ig/DM-AVRIL-2026/CodeSystem-TRE-R241-AideFinanciere.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-TRE-R241-AideFinanciere.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +118,9 @@
     <t>Count</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Code</t>
   </si>
   <si>
@@ -130,6 +133,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -139,13 +145,31 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
     <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>finess</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#finess</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts utilisés par FINESS+</t>
+  </si>
+  <si>
+    <t>boolean</t>
   </si>
   <si>
     <t>deprecationDate</t>
@@ -502,7 +526,9 @@
       <c r="A22" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -511,99 +537,119 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>43</v>
+      </c>
       <c r="C3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>39</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -618,51 +664,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2"/>
     </row>
